--- a/references/01 - Tai lieu du an/1. Ke hoach phat hieu yeu cau BTL (Elicitation)/Epic_UserStory.xlsx
+++ b/references/01 - Tai lieu du an/1. Ke hoach phat hieu yeu cau BTL (Elicitation)/Epic_UserStory.xlsx
@@ -1599,7 +1599,7 @@
     <t>ROADMAP v2.0</t>
   </si>
   <si>
-    <t>Phí gửi xe và thu hộ điện, nước, internet: Roadmap / Future Release, Won't-have cho phiên bản hiện tại. Không viết story.</t>
+    <t>Phí gửi xe và thu hộ điện, nước, internet: Roadmap / Future Release, Không sử dụng cho phiên bản hiện tại. Không viết story.</t>
   </si>
   <si>
     <t>Epics — BlueMoon v1.0</t>
@@ -2288,7 +2288,7 @@
     <t>ROADMAP</t>
   </si>
   <si>
-    <t>Won't-have cho v1.0. Không tạo Epic, Feature hay User Story. Mức phí ô tô trong đề bài cần xác nhận.</t>
+    <t>Không sử dụng cho v1.0. Không tạo Epic, Feature hay User Story. Mức phí ô tô trong đề bài cần xác nhận.</t>
   </si>
   <si>
     <t>—</t>
@@ -2306,7 +2306,7 @@
     <t>[Roadmap v2.0] Quản lý các khoản thu hộ điện, nước, internet theo thông báo của nhà cung cấp dịch vụ.</t>
   </si>
   <si>
-    <t>Won't-have cho v1.0. Không tạo Epic, Feature hay User Story.</t>
+    <t>Không sử dụng cho v1.0. Không tạo Epic, Feature hay User Story.</t>
   </si>
   <si>
     <t>Các mục được rà soát ngoài danh sách RAW (không có RAW; không chuyển thành story)</t>
